--- a/data/trans_orig/P43A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P43A-Provincia-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17321</t>
+          <t>16738</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36103</t>
+          <t>35213</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17321</t>
+          <t>16738</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36103</t>
+          <t>35213</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>38,81%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26335</t>
+          <t>26565</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46423</t>
+          <t>46452</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26335</t>
+          <t>26565</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46423</t>
+          <t>46452</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,2%</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>8366</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21065</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>8366</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21065</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,87%</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9165</t>
+          <t>9539</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24212</t>
+          <t>24684</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9165</t>
+          <t>9539</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24212</t>
+          <t>24684</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37358</t>
+          <t>37945</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61935</t>
+          <t>61850</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37358</t>
+          <t>37945</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>61935</t>
+          <t>61850</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,31%</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55075</t>
+          <t>54071</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80295</t>
+          <t>80550</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55075</t>
+          <t>54071</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80295</t>
+          <t>80550</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,69%</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35390</t>
+          <t>35951</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57777</t>
+          <t>59238</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35390</t>
+          <t>35951</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57777</t>
+          <t>59238</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,87%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>10699</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26401</t>
+          <t>27662</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>10699</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26401</t>
+          <t>27662</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20442</t>
+          <t>19331</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39028</t>
+          <t>38181</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20442</t>
+          <t>19331</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39028</t>
+          <t>38181</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,28%</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38964</t>
+          <t>38271</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60872</t>
+          <t>59797</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38964</t>
+          <t>38271</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>60872</t>
+          <t>59797</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,3%</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14924</t>
+          <t>15391</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32817</t>
+          <t>32830</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14924</t>
+          <t>15391</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32817</t>
+          <t>32830</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -1695,12 +1695,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24584</t>
+          <t>24613</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45405</t>
+          <t>46170</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24584</t>
+          <t>24613</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45405</t>
+          <t>46170</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>34,2%</t>
         </is>
       </c>
     </row>
@@ -1855,12 +1855,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38738</t>
+          <t>38981</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62021</t>
+          <t>61039</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38738</t>
+          <t>38981</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62021</t>
+          <t>61039</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,11%</t>
         </is>
       </c>
     </row>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29668</t>
+          <t>29687</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>50397</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29668</t>
+          <t>29687</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>50397</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,12%</t>
         </is>
       </c>
     </row>
@@ -2011,12 +2011,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28437</t>
+          <t>28672</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>48970</t>
+          <t>49059</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28437</t>
+          <t>28672</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>48970</t>
+          <t>49059</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,24%</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17759</t>
+          <t>17578</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34818</t>
+          <t>35589</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17759</t>
+          <t>17578</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34818</t>
+          <t>35589</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6973</t>
+          <t>6082</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19213</t>
+          <t>19138</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6973</t>
+          <t>6082</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19213</t>
+          <t>19138</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,18%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19690</t>
+          <t>20039</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>34627</t>
+          <t>35545</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19690</t>
+          <t>20039</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34627</t>
+          <t>35545</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>57,91%</t>
         </is>
       </c>
     </row>
@@ -2405,12 +2405,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8618</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22374</t>
+          <t>22809</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8618</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22374</t>
+          <t>22809</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>13076</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>13076</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -2643,12 +2643,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16594</t>
+          <t>17171</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>34434</t>
+          <t>33929</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16594</t>
+          <t>17171</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34434</t>
+          <t>33929</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>
@@ -2721,12 +2721,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>25823</t>
+          <t>25402</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>44258</t>
+          <t>44064</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>25823</t>
+          <t>25402</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>44258</t>
+          <t>44064</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -2799,12 +2799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>17947</t>
+          <t>17347</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>35662</t>
+          <t>34708</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17947</t>
+          <t>17347</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>35662</t>
+          <t>34708</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>32,71%</t>
         </is>
       </c>
     </row>
@@ -2877,12 +2877,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>14044</t>
+          <t>13935</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>30023</t>
+          <t>30632</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2912,12 +2912,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14044</t>
+          <t>13935</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>30023</t>
+          <t>30632</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -3037,12 +3037,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>58531</t>
+          <t>59117</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>88316</t>
+          <t>88597</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>58531</t>
+          <t>59117</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>88316</t>
+          <t>88597</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>74820</t>
+          <t>73758</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>105120</t>
+          <t>104079</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>74820</t>
+          <t>73758</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>105120</t>
+          <t>104079</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,73%</t>
         </is>
       </c>
     </row>
@@ -3193,12 +3193,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>48451</t>
+          <t>48835</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>77288</t>
+          <t>75320</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>48451</t>
+          <t>48835</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>77288</t>
+          <t>75320</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,31%</t>
         </is>
       </c>
     </row>
@@ -3271,12 +3271,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>39593</t>
+          <t>40701</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>66384</t>
+          <t>66750</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>39593</t>
+          <t>40701</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>66384</t>
+          <t>66750</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -3431,12 +3431,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>31057</t>
+          <t>31114</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>56117</t>
+          <t>55684</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>31057</t>
+          <t>31114</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>56117</t>
+          <t>55684</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -3509,12 +3509,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>89859</t>
+          <t>90107</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>120174</t>
+          <t>122198</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>89859</t>
+          <t>90107</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>120174</t>
+          <t>122198</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,93%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>57524</t>
+          <t>58117</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>87792</t>
+          <t>87763</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>57524</t>
+          <t>58117</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>87792</t>
+          <t>87763</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>35283</t>
+          <t>34642</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>61309</t>
+          <t>60469</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>35283</t>
+          <t>34642</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>61309</t>
+          <t>60469</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>272176</t>
+          <t>274444</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>337318</t>
+          <t>335864</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>272176</t>
+          <t>274444</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>337318</t>
+          <t>335864</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -3903,12 +3903,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>414272</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>486761</t>
+          <t>481869</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>414272</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>486761</t>
+          <t>481869</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,02%</t>
         </is>
       </c>
     </row>
@@ -3981,12 +3981,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>266117</t>
+          <t>266466</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>325962</t>
+          <t>325731</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>266117</t>
+          <t>266466</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>325962</t>
+          <t>325731</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -4059,12 +4059,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>195365</t>
+          <t>195391</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>249938</t>
+          <t>249488</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -4094,12 +4094,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>195365</t>
+          <t>195391</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>249938</t>
+          <t>249488</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25650</t>
+          <t>25828</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47415</t>
+          <t>47218</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25650</t>
+          <t>25828</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47415</t>
+          <t>47218</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -4472,12 +4472,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28262</t>
+          <t>28449</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51187</t>
+          <t>51770</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4487,12 +4487,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28262</t>
+          <t>28449</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51187</t>
+          <t>51770</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -4550,12 +4550,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33481</t>
+          <t>33198</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58257</t>
+          <t>57441</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4585,12 +4585,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33481</t>
+          <t>33198</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58257</t>
+          <t>57441</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4600,12 +4600,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,46%</t>
         </is>
       </c>
     </row>
@@ -4628,12 +4628,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17373</t>
+          <t>17273</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38913</t>
+          <t>38145</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17373</t>
+          <t>17273</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38913</t>
+          <t>38145</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -4788,12 +4788,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28032</t>
+          <t>28979</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53168</t>
+          <t>53358</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28032</t>
+          <t>28979</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>53168</t>
+          <t>53358</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,44%</t>
         </is>
       </c>
     </row>
@@ -4866,12 +4866,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75141</t>
+          <t>75068</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105014</t>
+          <t>105974</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4881,12 +4881,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75141</t>
+          <t>75068</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105014</t>
+          <t>105974</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4916,12 +4916,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,54%</t>
         </is>
       </c>
     </row>
@@ -4944,12 +4944,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42075</t>
+          <t>41353</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68693</t>
+          <t>68150</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4959,12 +4959,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42075</t>
+          <t>41353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68693</t>
+          <t>68150</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4994,12 +4994,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -5022,12 +5022,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23996</t>
+          <t>23369</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47257</t>
+          <t>46792</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5057,12 +5057,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23996</t>
+          <t>23369</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47257</t>
+          <t>46792</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14949</t>
+          <t>13710</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35293</t>
+          <t>33600</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14949</t>
+          <t>13710</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35293</t>
+          <t>33600</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -5260,12 +5260,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61200</t>
+          <t>61376</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>87266</t>
+          <t>87290</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5275,12 +5275,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>61200</t>
+          <t>61376</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>87266</t>
+          <t>87290</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,91%</t>
         </is>
       </c>
     </row>
@@ -5338,12 +5338,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28392</t>
+          <t>27089</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50468</t>
+          <t>49168</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28392</t>
+          <t>27089</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50468</t>
+          <t>49168</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5388,12 +5388,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>30,93%</t>
         </is>
       </c>
     </row>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15046</t>
+          <t>14875</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34656</t>
+          <t>33433</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5451,12 +5451,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15046</t>
+          <t>14875</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34656</t>
+          <t>33433</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -5576,12 +5576,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22548</t>
+          <t>22374</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43457</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22548</t>
+          <t>22374</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43457</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -5654,12 +5654,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>54870</t>
+          <t>54999</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>81532</t>
+          <t>81737</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54870</t>
+          <t>54999</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>81532</t>
+          <t>81737</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49599</t>
+          <t>49742</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>75978</t>
+          <t>75861</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49599</t>
+          <t>49742</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>75978</t>
+          <t>75861</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,53%</t>
         </is>
       </c>
     </row>
@@ -5810,12 +5810,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17304</t>
+          <t>17564</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36149</t>
+          <t>36506</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5845,12 +5845,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17304</t>
+          <t>17564</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36149</t>
+          <t>36506</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -5970,12 +5970,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>16967</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>34076</t>
+          <t>34231</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5985,12 +5985,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6005,12 +6005,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>16967</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34076</t>
+          <t>34231</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,64%</t>
         </is>
       </c>
     </row>
@@ -6048,12 +6048,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29963</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50728</t>
+          <t>49494</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6063,12 +6063,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29963</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50728</t>
+          <t>49494</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6098,12 +6098,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>47,19%</t>
         </is>
       </c>
     </row>
@@ -6126,12 +6126,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22021</t>
+          <t>21410</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>39944</t>
+          <t>40302</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6141,12 +6141,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>22021</t>
+          <t>21410</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>39944</t>
+          <t>40302</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6176,12 +6176,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,43%</t>
         </is>
       </c>
     </row>
@@ -6204,12 +6204,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18197</t>
+          <t>18415</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6219,12 +6219,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>18197</t>
+          <t>18415</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6254,12 +6254,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,56%</t>
         </is>
       </c>
     </row>
@@ -6364,12 +6364,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29348</t>
+          <t>29258</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>50385</t>
+          <t>49331</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>29348</t>
+          <t>29258</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>50385</t>
+          <t>49331</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -6442,12 +6442,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>44651</t>
+          <t>44471</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>67973</t>
+          <t>66392</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>44651</t>
+          <t>44471</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>67973</t>
+          <t>66392</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>48,76%</t>
         </is>
       </c>
     </row>
@@ -6520,12 +6520,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19331</t>
+          <t>20372</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>39232</t>
+          <t>39590</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -6555,12 +6555,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>19331</t>
+          <t>20372</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>39232</t>
+          <t>39590</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,08%</t>
         </is>
       </c>
     </row>
@@ -6598,12 +6598,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>20051</t>
+          <t>20005</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20051</t>
+          <t>20005</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -6648,12 +6648,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>56087</t>
+          <t>56117</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>87929</t>
+          <t>87061</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>56087</t>
+          <t>56117</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>87929</t>
+          <t>87061</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -6836,12 +6836,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>114341</t>
+          <t>113751</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>152909</t>
+          <t>152535</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>114341</t>
+          <t>113751</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>152909</t>
+          <t>152535</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,35%</t>
         </is>
       </c>
     </row>
@@ -6914,12 +6914,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>70083</t>
+          <t>68315</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>103345</t>
+          <t>103681</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>70083</t>
+          <t>68315</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>103345</t>
+          <t>103681</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -6992,12 +6992,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>49046</t>
+          <t>48769</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>81229</t>
+          <t>80428</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>49046</t>
+          <t>48769</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>81229</t>
+          <t>80428</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -7152,12 +7152,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>62065</t>
+          <t>61048</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>93520</t>
+          <t>92669</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -7167,12 +7167,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>62065</t>
+          <t>61048</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>93520</t>
+          <t>92669</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -7230,12 +7230,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>120073</t>
+          <t>117778</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>158834</t>
+          <t>155880</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -7245,12 +7245,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>120073</t>
+          <t>117778</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>158834</t>
+          <t>155880</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -7280,12 +7280,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,16%</t>
         </is>
       </c>
     </row>
@@ -7308,12 +7308,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>82818</t>
+          <t>83447</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>116608</t>
+          <t>118201</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>82818</t>
+          <t>83447</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>116608</t>
+          <t>118201</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -7386,12 +7386,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>36234</t>
+          <t>35166</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>61996</t>
+          <t>61903</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>36234</t>
+          <t>35166</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>61996</t>
+          <t>61903</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>308016</t>
+          <t>309091</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>378446</t>
+          <t>377771</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>308016</t>
+          <t>309091</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>378446</t>
+          <t>377771</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -7624,12 +7624,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>597342</t>
+          <t>598796</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>677877</t>
+          <t>677245</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -7659,12 +7659,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>597342</t>
+          <t>598796</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>677877</t>
+          <t>677245</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -7674,12 +7674,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,7%</t>
         </is>
       </c>
     </row>
@@ -7702,12 +7702,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>403737</t>
+          <t>406435</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>477365</t>
+          <t>480577</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>403737</t>
+          <t>406435</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>477365</t>
+          <t>480577</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -7780,12 +7780,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>212358</t>
+          <t>213239</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>274247</t>
+          <t>272911</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -7795,12 +7795,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -7815,12 +7815,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>212358</t>
+          <t>213239</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>274247</t>
+          <t>272911</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -8115,12 +8115,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27170</t>
+          <t>27190</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49310</t>
+          <t>49791</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27170</t>
+          <t>27190</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49310</t>
+          <t>49791</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,48%</t>
         </is>
       </c>
     </row>
@@ -8193,12 +8193,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31219</t>
+          <t>31856</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53789</t>
+          <t>53827</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31219</t>
+          <t>31856</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53789</t>
+          <t>53827</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,27%</t>
         </is>
       </c>
     </row>
@@ -8271,12 +8271,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38133</t>
+          <t>37980</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>61665</t>
+          <t>61351</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38133</t>
+          <t>37980</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61665</t>
+          <t>61351</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,48%</t>
         </is>
       </c>
     </row>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9893</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26470</t>
+          <t>25794</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8364,12 +8364,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8384,12 +8384,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9893</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26470</t>
+          <t>25794</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -8509,12 +8509,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39944</t>
+          <t>41668</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67496</t>
+          <t>68499</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8524,12 +8524,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8544,12 +8544,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39944</t>
+          <t>41668</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>67496</t>
+          <t>68499</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -8587,12 +8587,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>120811</t>
+          <t>120804</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155709</t>
+          <t>154760</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8622,12 +8622,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>120811</t>
+          <t>120804</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>155709</t>
+          <t>154760</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,14%</t>
         </is>
       </c>
     </row>
@@ -8665,12 +8665,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34059</t>
+          <t>34021</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59780</t>
+          <t>58353</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34059</t>
+          <t>34021</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59780</t>
+          <t>58353</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8715,12 +8715,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -8743,12 +8743,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19056</t>
+          <t>19110</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40771</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19056</t>
+          <t>19110</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40771</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -8903,12 +8903,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31513</t>
+          <t>31990</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54701</t>
+          <t>54294</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31513</t>
+          <t>31990</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54701</t>
+          <t>54294</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8953,12 +8953,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>65900</t>
+          <t>65213</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92444</t>
+          <t>92190</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>65900</t>
+          <t>65213</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>92444</t>
+          <t>92190</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,04%</t>
         </is>
       </c>
     </row>
@@ -9059,12 +9059,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34875</t>
+          <t>34967</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58905</t>
+          <t>58609</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9074,12 +9074,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34875</t>
+          <t>34967</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58905</t>
+          <t>58609</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,18%</t>
         </is>
       </c>
     </row>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12849</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30568</t>
+          <t>30815</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9172,12 +9172,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12849</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30568</t>
+          <t>30815</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -9297,12 +9297,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37659</t>
+          <t>37303</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63383</t>
+          <t>62457</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9312,12 +9312,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9332,12 +9332,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37659</t>
+          <t>37303</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63383</t>
+          <t>62457</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9347,12 +9347,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -9375,12 +9375,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>63591</t>
+          <t>63090</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91559</t>
+          <t>91645</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9410,12 +9410,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>63591</t>
+          <t>63090</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>91559</t>
+          <t>91645</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,93%</t>
         </is>
       </c>
     </row>
@@ -9453,12 +9453,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38204</t>
+          <t>38398</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>63513</t>
+          <t>63860</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9468,12 +9468,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9488,12 +9488,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>38204</t>
+          <t>38398</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>63513</t>
+          <t>63860</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9503,12 +9503,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,31%</t>
         </is>
       </c>
     </row>
@@ -9531,12 +9531,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18367</t>
+          <t>17827</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37886</t>
+          <t>37798</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9566,12 +9566,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18367</t>
+          <t>17827</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37886</t>
+          <t>37798</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9581,12 +9581,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -9691,12 +9691,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>37508</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>58519</t>
+          <t>57786</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9706,12 +9706,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9726,12 +9726,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>37508</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>58519</t>
+          <t>57786</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9741,12 +9741,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,38%</t>
         </is>
       </c>
     </row>
@@ -9769,12 +9769,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32183</t>
+          <t>31951</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53689</t>
+          <t>53438</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9784,12 +9784,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32183</t>
+          <t>31951</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>53689</t>
+          <t>53438</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9819,12 +9819,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,59%</t>
         </is>
       </c>
     </row>
@@ -9847,12 +9847,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25427</t>
+          <t>26325</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9862,12 +9862,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25427</t>
+          <t>26325</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9897,12 +9897,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,95%</t>
         </is>
       </c>
     </row>
@@ -9925,12 +9925,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>3932</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>14757</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9940,12 +9940,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>3932</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>14757</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -10085,12 +10085,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>31986</t>
+          <t>30132</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>53963</t>
+          <t>52465</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10100,12 +10100,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10120,12 +10120,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>31986</t>
+          <t>30132</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>53963</t>
+          <t>52465</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10135,12 +10135,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>
@@ -10163,12 +10163,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>37501</t>
+          <t>38060</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>61138</t>
+          <t>60966</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10198,12 +10198,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>37501</t>
+          <t>38060</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>61138</t>
+          <t>60966</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10213,12 +10213,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,68%</t>
         </is>
       </c>
     </row>
@@ -10241,12 +10241,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13780</t>
+          <t>14119</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>30395</t>
+          <t>31725</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>13780</t>
+          <t>14119</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>30395</t>
+          <t>31725</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>16326</t>
+          <t>16327</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>34470</t>
+          <t>34139</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16326</t>
+          <t>16327</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>34470</t>
+          <t>34139</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -10479,12 +10479,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>47644</t>
+          <t>47695</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>77769</t>
+          <t>78128</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10494,12 +10494,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10514,12 +10514,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>47644</t>
+          <t>47695</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>77769</t>
+          <t>78128</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,08%</t>
         </is>
       </c>
     </row>
@@ -10557,12 +10557,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>105889</t>
+          <t>105621</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>141817</t>
+          <t>140536</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10572,12 +10572,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10592,12 +10592,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>105889</t>
+          <t>105621</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>141817</t>
+          <t>140536</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10607,12 +10607,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>48,71%</t>
         </is>
       </c>
     </row>
@@ -10635,12 +10635,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>52790</t>
+          <t>54244</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>82135</t>
+          <t>84264</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10650,12 +10650,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10670,12 +10670,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>52790</t>
+          <t>54244</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>82135</t>
+          <t>84264</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10685,12 +10685,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>29,21%</t>
         </is>
       </c>
     </row>
@@ -10713,12 +10713,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>23513</t>
+          <t>24735</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>49279</t>
+          <t>48130</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10728,12 +10728,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>23513</t>
+          <t>24735</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>49279</t>
+          <t>48130</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,68%</t>
         </is>
       </c>
     </row>
@@ -10873,12 +10873,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>77498</t>
+          <t>77849</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>116456</t>
+          <t>118279</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10888,12 +10888,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>77498</t>
+          <t>77849</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>116456</t>
+          <t>118279</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -10923,12 +10923,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -10951,12 +10951,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>135680</t>
+          <t>132933</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>176902</t>
+          <t>174562</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10966,12 +10966,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>135680</t>
+          <t>132933</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>176902</t>
+          <t>174562</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11001,12 +11001,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,17%</t>
         </is>
       </c>
     </row>
@@ -11029,12 +11029,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>96396</t>
+          <t>94543</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>135175</t>
+          <t>132784</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11064,12 +11064,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>96396</t>
+          <t>94543</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>135175</t>
+          <t>132784</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11079,12 +11079,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -11107,12 +11107,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>36506</t>
+          <t>34959</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>62263</t>
+          <t>64406</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11142,12 +11142,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>36506</t>
+          <t>34959</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>62263</t>
+          <t>64406</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -11267,12 +11267,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>393266</t>
+          <t>388794</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>465610</t>
+          <t>467388</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11302,12 +11302,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>393266</t>
+          <t>388794</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>465610</t>
+          <t>467388</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11317,12 +11317,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,61%</t>
         </is>
       </c>
     </row>
@@ -11345,12 +11345,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>658788</t>
+          <t>664508</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>746128</t>
+          <t>747576</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>658788</t>
+          <t>664508</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>746128</t>
+          <t>747576</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,57%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>378201</t>
+          <t>376572</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>450296</t>
+          <t>450291</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>378201</t>
+          <t>376572</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>450296</t>
+          <t>450291</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>183090</t>
+          <t>184251</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>237087</t>
+          <t>239535</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>183090</t>
+          <t>184251</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>237087</t>
+          <t>239535</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -11831,32 +11831,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>35198</t>
+          <t>36067</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27140</t>
+          <t>29248</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42293</t>
+          <t>43755</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11866,32 +11866,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>35198</t>
+          <t>36067</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27140</t>
+          <t>29248</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42293</t>
+          <t>43755</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -11909,32 +11909,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41505</t>
+          <t>43697</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34220</t>
+          <t>37074</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49228</t>
+          <t>51869</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11944,32 +11944,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>41505</t>
+          <t>43697</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34220</t>
+          <t>37074</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49228</t>
+          <t>51869</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -11987,32 +11987,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14584</t>
+          <t>14658</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>9811</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20411</t>
+          <t>19384</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -12022,32 +12022,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14584</t>
+          <t>14658</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>9811</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20411</t>
+          <t>19384</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -12065,32 +12065,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24805</t>
+          <t>24334</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18564</t>
+          <t>18688</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31770</t>
+          <t>30950</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12100,32 +12100,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24805</t>
+          <t>24334</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18564</t>
+          <t>18688</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31770</t>
+          <t>30950</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>26,06%</t>
         </is>
       </c>
     </row>
@@ -12143,17 +12143,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>116092</t>
+          <t>118755</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>116092</t>
+          <t>118755</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>116092</t>
+          <t>118755</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12178,17 +12178,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>116092</t>
+          <t>118755</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>116092</t>
+          <t>118755</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>116092</t>
+          <t>118755</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12225,17 +12225,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>107149</t>
+          <t>111192</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94780</t>
+          <t>98989</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>119137</t>
+          <t>123736</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12245,12 +12245,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12260,17 +12260,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>107149</t>
+          <t>111192</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>94780</t>
+          <t>98989</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>119137</t>
+          <t>123736</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12280,12 +12280,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>54,06%</t>
         </is>
       </c>
     </row>
@@ -12303,32 +12303,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>66129</t>
+          <t>67597</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55946</t>
+          <t>56482</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78222</t>
+          <t>80109</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12338,32 +12338,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>66129</t>
+          <t>67597</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55946</t>
+          <t>56482</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78222</t>
+          <t>80109</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,0%</t>
         </is>
       </c>
     </row>
@@ -12381,32 +12381,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25402</t>
+          <t>25191</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18556</t>
+          <t>18301</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33909</t>
+          <t>33722</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12416,32 +12416,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25402</t>
+          <t>25191</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18556</t>
+          <t>18301</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33909</t>
+          <t>33722</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -12459,32 +12459,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21894</t>
+          <t>24891</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15349</t>
+          <t>17476</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29712</t>
+          <t>33311</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12494,32 +12494,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21894</t>
+          <t>24891</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15349</t>
+          <t>17476</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29712</t>
+          <t>33311</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -12537,17 +12537,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>220574</t>
+          <t>228871</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>220574</t>
+          <t>228871</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>220574</t>
+          <t>228871</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12572,17 +12572,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>220574</t>
+          <t>228871</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>220574</t>
+          <t>228871</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>220574</t>
+          <t>228871</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12619,32 +12619,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>50491</t>
+          <t>51503</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42074</t>
+          <t>43464</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59173</t>
+          <t>60576</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12654,32 +12654,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>50491</t>
+          <t>51503</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42074</t>
+          <t>43464</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59173</t>
+          <t>60576</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>44,16%</t>
         </is>
       </c>
     </row>
@@ -12697,32 +12697,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35708</t>
+          <t>36197</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28650</t>
+          <t>28138</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44458</t>
+          <t>43661</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12732,32 +12732,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35708</t>
+          <t>36197</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28650</t>
+          <t>28138</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44458</t>
+          <t>43661</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>31,83%</t>
         </is>
       </c>
     </row>
@@ -12775,32 +12775,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>27457</t>
+          <t>28172</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20935</t>
+          <t>21377</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35691</t>
+          <t>36200</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12810,32 +12810,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>27457</t>
+          <t>28172</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20935</t>
+          <t>21377</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35691</t>
+          <t>36200</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -12853,32 +12853,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21281</t>
+          <t>21309</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15178</t>
+          <t>14852</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29504</t>
+          <t>29178</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12888,32 +12888,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21281</t>
+          <t>21309</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15178</t>
+          <t>14852</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29504</t>
+          <t>29178</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -12931,17 +12931,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>134937</t>
+          <t>137181</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>134937</t>
+          <t>137181</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>134937</t>
+          <t>137181</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12966,17 +12966,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>134937</t>
+          <t>137181</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>134937</t>
+          <t>137181</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>134937</t>
+          <t>137181</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>93788</t>
+          <t>65662</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>70378</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>131496</t>
+          <t>75212</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13048,32 +13048,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>93788</t>
+          <t>65662</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>70378</t>
+          <t>55864</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>131496</t>
+          <t>75212</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>45,36%</t>
         </is>
       </c>
     </row>
@@ -13091,32 +13091,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>46741</t>
+          <t>52934</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26208</t>
+          <t>43847</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>61467</t>
+          <t>62963</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>46741</t>
+          <t>52934</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26208</t>
+          <t>43847</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61467</t>
+          <t>62963</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>37,97%</t>
         </is>
       </c>
     </row>
@@ -13169,32 +13169,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22308</t>
+          <t>26773</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11615</t>
+          <t>20021</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31525</t>
+          <t>35399</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13204,32 +13204,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22308</t>
+          <t>26773</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11615</t>
+          <t>20021</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31525</t>
+          <t>35399</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -13247,32 +13247,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>18530</t>
+          <t>20456</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>14533</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26826</t>
+          <t>27318</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13282,32 +13282,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>18530</t>
+          <t>20456</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>14533</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26826</t>
+          <t>27318</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -13325,17 +13325,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>181368</t>
+          <t>165825</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>181368</t>
+          <t>165825</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>181368</t>
+          <t>165825</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13360,17 +13360,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>181368</t>
+          <t>165825</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>181368</t>
+          <t>165825</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>181368</t>
+          <t>165825</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13407,32 +13407,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>34133</t>
+          <t>35185</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28587</t>
+          <t>28951</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40686</t>
+          <t>41158</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13442,32 +13442,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>34133</t>
+          <t>35185</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>28587</t>
+          <t>28951</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>40686</t>
+          <t>41158</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -13485,32 +13485,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>42620</t>
+          <t>46691</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36126</t>
+          <t>40143</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49165</t>
+          <t>54050</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13520,32 +13520,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>42620</t>
+          <t>46691</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36126</t>
+          <t>40143</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49165</t>
+          <t>54050</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>45,1%</t>
         </is>
       </c>
     </row>
@@ -13563,32 +13563,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>30714</t>
+          <t>33244</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25311</t>
+          <t>26965</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36430</t>
+          <t>39525</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13598,32 +13598,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>30714</t>
+          <t>33244</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>25311</t>
+          <t>26965</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>36430</t>
+          <t>39525</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -13641,32 +13641,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7771</t>
+          <t>7963</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -13676,32 +13676,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7771</t>
+          <t>7963</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -13719,17 +13719,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>111978</t>
+          <t>119840</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>111978</t>
+          <t>119840</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>111978</t>
+          <t>119840</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13754,17 +13754,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>111978</t>
+          <t>119840</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>111978</t>
+          <t>119840</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>111978</t>
+          <t>119840</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13801,32 +13801,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>34856</t>
+          <t>35791</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>28623</t>
+          <t>29484</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>41644</t>
+          <t>42663</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13836,32 +13836,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>34856</t>
+          <t>35791</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28623</t>
+          <t>29484</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>41644</t>
+          <t>42663</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -13879,32 +13879,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>33313</t>
+          <t>34948</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>26959</t>
+          <t>28863</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40824</t>
+          <t>42361</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13914,32 +13914,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>33313</t>
+          <t>34948</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>26959</t>
+          <t>28863</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>40824</t>
+          <t>42361</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,73%</t>
         </is>
       </c>
     </row>
@@ -13957,32 +13957,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>32422</t>
+          <t>33380</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>26434</t>
+          <t>26199</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>39746</t>
+          <t>40452</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13992,32 +13992,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>32422</t>
+          <t>33380</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>26434</t>
+          <t>26199</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>39746</t>
+          <t>40452</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -14035,32 +14035,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>11163</t>
+          <t>11209</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>7129</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>16739</t>
+          <t>16256</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14070,32 +14070,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>11163</t>
+          <t>11209</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>7129</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16739</t>
+          <t>16256</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -14113,17 +14113,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>111753</t>
+          <t>115329</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>111753</t>
+          <t>115329</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>111753</t>
+          <t>115329</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14148,17 +14148,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>111753</t>
+          <t>115329</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>111753</t>
+          <t>115329</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>111753</t>
+          <t>115329</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -14195,32 +14195,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>67331</t>
+          <t>80045</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>23274</t>
+          <t>66864</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>122795</t>
+          <t>94858</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14230,32 +14230,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>67331</t>
+          <t>80045</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>23274</t>
+          <t>66864</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>122795</t>
+          <t>94858</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -14273,32 +14273,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>278086</t>
+          <t>86613</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>119527</t>
+          <t>73036</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>409825</t>
+          <t>101507</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14308,32 +14308,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>278086</t>
+          <t>86613</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>119527</t>
+          <t>73036</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>409825</t>
+          <t>101507</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>31,07%</t>
         </is>
       </c>
     </row>
@@ -14351,32 +14351,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>89735</t>
+          <t>103782</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>90207</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>163052</t>
+          <t>119820</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14386,32 +14386,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>89735</t>
+          <t>103782</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>90207</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>163052</t>
+          <t>119820</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>36,68%</t>
         </is>
       </c>
     </row>
@@ -14429,32 +14429,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>49037</t>
+          <t>56242</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>16390</t>
+          <t>43854</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>90235</t>
+          <t>70650</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14464,32 +14464,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>49037</t>
+          <t>56242</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>16390</t>
+          <t>43854</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>90235</t>
+          <t>70650</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -14507,17 +14507,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>484189</t>
+          <t>326682</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>484189</t>
+          <t>326682</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>484189</t>
+          <t>326682</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14542,17 +14542,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>484189</t>
+          <t>326682</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>484189</t>
+          <t>326682</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>484189</t>
+          <t>326682</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14589,32 +14589,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>58742</t>
+          <t>66724</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>49884</t>
+          <t>56131</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>68641</t>
+          <t>79155</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -14624,32 +14624,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>58742</t>
+          <t>66724</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>49884</t>
+          <t>56131</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>68641</t>
+          <t>79155</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,83%</t>
         </is>
       </c>
     </row>
@@ -14667,32 +14667,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>76463</t>
+          <t>89106</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>65902</t>
+          <t>77446</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>87278</t>
+          <t>102926</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14702,32 +14702,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>76463</t>
+          <t>89106</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>65902</t>
+          <t>77446</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>87278</t>
+          <t>102926</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>41,39%</t>
         </is>
       </c>
     </row>
@@ -14745,32 +14745,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>67079</t>
+          <t>76011</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>56635</t>
+          <t>63974</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>78853</t>
+          <t>87896</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14780,32 +14780,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>67079</t>
+          <t>76011</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>56635</t>
+          <t>63974</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>78853</t>
+          <t>87896</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>35,34%</t>
         </is>
       </c>
     </row>
@@ -14823,32 +14823,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>15276</t>
+          <t>16844</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>10145</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>22028</t>
+          <t>24441</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -14858,32 +14858,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>15276</t>
+          <t>16844</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>10145</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>22028</t>
+          <t>24441</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -14901,17 +14901,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>217559</t>
+          <t>248685</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>217559</t>
+          <t>248685</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>217559</t>
+          <t>248685</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -14936,17 +14936,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>217559</t>
+          <t>248685</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>217559</t>
+          <t>248685</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>217559</t>
+          <t>248685</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -14983,32 +14983,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>481689</t>
+          <t>482169</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>322657</t>
+          <t>451440</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>574275</t>
+          <t>509621</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15018,32 +15018,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>481689</t>
+          <t>482169</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>322657</t>
+          <t>451440</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>574275</t>
+          <t>509621</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -15061,32 +15061,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>620565</t>
+          <t>457782</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>466801</t>
+          <t>431618</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>956590</t>
+          <t>487799</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -15096,32 +15096,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>620565</t>
+          <t>457782</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>466801</t>
+          <t>431618</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>956590</t>
+          <t>487799</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -15139,32 +15139,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>309699</t>
+          <t>341211</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>202472</t>
+          <t>313123</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>364691</t>
+          <t>367224</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -15174,32 +15174,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>309699</t>
+          <t>341211</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>202472</t>
+          <t>313123</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>364691</t>
+          <t>367224</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -15217,32 +15217,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>166496</t>
+          <t>180005</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>109433</t>
+          <t>162379</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>199522</t>
+          <t>201852</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -15252,32 +15252,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>166496</t>
+          <t>180005</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>109433</t>
+          <t>162379</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>199522</t>
+          <t>201852</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -15295,17 +15295,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1578449</t>
+          <t>1461168</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1578449</t>
+          <t>1461168</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1578449</t>
+          <t>1461168</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -15330,17 +15330,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1578449</t>
+          <t>1461168</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1578449</t>
+          <t>1461168</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1578449</t>
+          <t>1461168</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
